--- a/data/India_300_National_Initiatives_History_2_2.xlsx
+++ b/data/India_300_National_Initiatives_History_2_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895D33DC-7D5A-487E-B3A2-E73EB3251077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE372CD-3CB1-4F7F-9107-8506A0B67896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Year</t>
   </si>
@@ -52,37 +52,10 @@
     <t>Proof Link 3</t>
   </si>
   <si>
-    <t>https://www.thehindu.com/</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
     <t>Central Vista Redevelopment &amp; New Parliament</t>
-  </si>
-  <si>
-    <t>The strategic development of this national infrastructure represents one of the most critical imperatives for India since its independence. Historically, Indian developmental strategy defensively presumed that a slow, steady approach would suffice. However, over the subsequent decades, the geopolitical and economic landscape evolved dramatically and dangerously. Adversarial nations embarked on massive, rapid modernization, constructing dense networks of dual-use highways, high-speed rail lines, military-grade airbases, and mega-dams. This massive asymmetry gave adversaries the capability to dominate regional geopolitics and supply chains, while Indian capabilities lagged. Therefore, achieving logistical and economic parity through this infrastructure is vitally important for deterrence and survival. It is essential for sustaining economic outposts and military strongholds in critical geographic choke points. Furthermore, these projects provide all-weather, year-round connectivity and base-load energy to forward areas and industrial hubs. Without them, the nation remains completely isolated and dependent on exorbitant foreign supply lines. Beyond pure logistics, these infrastructure initiatives are crucially important for asserting territorial and economic sovereignty. Under international norms, the administrative control, connectivity, and civilian habitation of regions heavily strengthen a nation's sovereign claims. By providing robust connectivity and energy, the government can implement developmental programs, effectively reversing the dangerous trend of out-migration from communities who previously lacked access to basic healthcare, education, and markets. By ensuring these villages and industrial towns thrive economically, India reinforces its absolute first line of defense—its own citizens living securely and prosperously. The integration of civilian populations into the national grid creates a formidable bulwark against enemy psychological warfare and demographic manipulation, strategies frequently employed by adversaries. Ultimately, shifting from a defensive posture to an 'offensive defense' and economic powerhouse doctrine requires physical infrastructure capable of supporting modern mechanized operations and rapid industrial surges immune to global sanctions. This unified network is the physical manifestation of India's strategic resolve, acting as a direct deterrent to aggressive salami-slicing tactics, ensuring rapid deployment capabilities, and securing the socio-economic future of marginalized populations. The sheer survival of India's territorial integrity and economic independence hinges entirely on the completion and continuous expansion of this ecosystem, permanently altering the strategic calculus of the region. Without this infrastructure, the nation remains chronically exposed to territorial attrition, military coercion, and severe diplomatic disadvantages during bilateral negotiations. This robust network fundamentally transforms India from a passive observer into an active, formidable global force. The realization of Central Vista Redevelopment &amp; New Parliament is therefore non-negotiable. This absolute necessity cannot be understated in modern strategic contexts. The geopolitical and macroeconomic survival of the nation hinges directly on the timely and unhindered execution of this core infrastructure. Delaying such initiatives poses a catastrophic threat to the developmental trajectory of the country, leaving it vulnerable to external pressures and internal stagnation. Every single day of delay exponentially compounds the financial and strategic burden borne by the Indian state. The realization of Central Vista Redevelopment &amp; New Parliament is therefore non-negotiable. This absolute necessity cannot be understated in modern strategic contexts. The geopolitical and macroeconomic survival of the nation hinges directly on the timely and unhindered execution of this core infrastructure. Delaying such initiatives poses a catastrophic threat to the developmental trajectory of the country, leaving it vulnerable to external pressures and internal stagnation. Every single day of delay exponentially compounds the financial and strategic burden borne by the Indian state.</t>
-  </si>
-  <si>
-    <t>Rajeev Suri / Heritage &amp; Environmental Activists</t>
-  </si>
-  <si>
-    <t>Activists sought a stay citing violations in DDA land-use change, lack of public consultation, and flaws in the MoEF environmental clearance. In Jan 2021, a 2:1 SC majority upheld the project, stating courts cannot dictate executive policy or esthetics, and statutory procedures were followed.</t>
-  </si>
-  <si>
-    <t>Project completed, New Parliament inaugurated</t>
-  </si>
-  <si>
-    <t>Months of legal stays</t>
-  </si>
-  <si>
-    <t>The chronic delay in the execution of this strategic infrastructure has had profound, multidimensional repercussions on India's national security, economic resources, and diplomatic leverage over the past several decades. The genesis of these delays largely stemmed from extreme bureaucratic paralysis, stringent and highly inflexible environmental clearance processes, and a complete lack of inter-ministerial coordination. Consequently, vital projects conceptualized years ago remained stalled on paper for over a decade. The most immediate and severe effect of this delay manifested during critical military and economic crises, where the stark asymmetry in infrastructure allowed adversaries to rapidly deploy and establish entrenched positions, while Indian forces and industries faced severe logistical bottlenecks. In many sectors, the lack of robust networks meant crucial tactical response times were lost. Because India lacked the infrastructure to rapidly counter-mobilize or ramp up production, it was forced into reactive, protracted standoffs rather than proactive deterrence. Economically, the delays inflicted a massive, bleeding wound on the national budget. Because projects could not be supplied or completed efficiently, the state was forced to conduct continuous, massive stop-gap operations. Relying on outdated methods and emergency imports costs exponentially more than domestic production and land transport. Billions of rupees that could have been invested in modernizing technological platforms were instead burned on basic logistics and foreign procurement just to keep the economy afloat over consecutive decades. Furthermore, the infrastructure projects themselves suffered massive cost overruns; estimates escalated by 400% to 500% due to inflation, revised alignments, and extended contractor mobilizations over a 15-year period. Diplomatically, the delay heavily weakened India's negotiating position during bilateral talks. Adversaries, operating from a position of absolute infrastructural superiority, routinely ignored past protocols, knowing India lacked the logistical backbone to enforce them aggressively across all sectors simultaneously. The delayed integration of vital regions also led to the socio-economic isolation of communities, causing out-migration that left strategic 'empty zones' which foreign propaganda and demographic engineering sought to exploit. By stalling these projects over environmental concerns—such as intense legal battles over land use or tree felling—the nation inadvertently jeopardized the very foundations that protect its interior environments. The lost decade of development allowed adversaries to permanently alter the tactical reality on the ground, forcing India to now engage in a frantic, high-cost race to catch up under the constant shadow of a two-front war and economic blockade, struggling to close an infrastructural gap that should have been bridged decades ago. This immense failure to act promptly has fundamentally forced the nation to spend vast reserves of its capital budget on reactive structural fortifications rather than offensive technological acquisitions, severely stunting overall modernization. The realization of Central Vista Redevelopment &amp; New Parliament is therefore non-negotiable. This absolute necessity cannot be understated in modern strategic contexts. The geopolitical and macroeconomic survival of the nation hinges directly on the timely and unhindered execution of this core infrastructure. Delaying such initiatives poses a catastrophic threat to the developmental trajectory of the country, leaving it vulnerable to external pressures and internal stagnation. Every single day of delay exponentially compounds the financial and strategic burden borne by the Indian state. The realization of Central Vista Redevelopment &amp; New Parliament is therefore non-negotiable. This absolute necessity cannot be understated in modern strategic contexts. The geopolitical and macroeconomic survival of the nation hinges directly on the timely and unhindered execution of this core infrastructure. Delaying such initiatives poses a catastrophic threat to the developmental trajectory of the country, leaving it vulnerable to external pressures and internal stagnation. Every single day of delay exponentially compounds the financial and strategic burden borne by the Indian state.</t>
-  </si>
-  <si>
-    <t>https://indiankanoon.org/doc/31835695/</t>
-  </si>
-  <si>
-    <t>https://centralvista.gov.in/</t>
   </si>
   <si>
     <t>Abrogation of Article 370 and Reorganisation of Jammu &amp; Kashmir</t>
@@ -188,6 +161,41 @@
   </si>
   <si>
     <t>https://www.thehindu.com/news/national/centre-moves-supreme-court-to-stay-hearings-on-great-nicobar-project/article71525280.ece</t>
+  </si>
+  <si>
+    <t>The Central Vista Redevelopment is a vital assertion of India’s sovereign state capacity, democratic dignity, and strategic modernization. For nearly a century, the republic operated out of colonial-era structures commissioned in the 1920s under imperial rule—relics designed for an imperial council rather than an assertive, nuclear-armed democracy representing 1.4 billion citizens. The old Parliament suffered from severe architectural fatigue, non-compliance with seismic Zone IV and V safety norms, critical fire vulnerabilities, and cramped legislative chambers incapable of accommodating future democratic representation following delimitation.
+Administratively, executive governance was crippled by being scattered across more than 47 dilapidated buildings and temporary World War II barracks. This fragmentation cost the national exchequer upwards of ₹1,000 crore annually in rental leases, wasteful inter-ministerial physical transit, and logistical bottlenecks. The new development eliminates these operational inefficiencies by establishing a consolidated, subterranean-linked administrative core. It integrates cutting-edge cryptographic and paperless digital infrastructure, fortified physical command centers, and green-certified energy designs, shedding the legacy of colonial subservience and equipping the Indian state to govern with the speed, synergy, and authority demanded of a 21st-century global power.</t>
+  </si>
+  <si>
+    <t>Indian National Congress, CPI(M), CPI, AAP, TMC, DMK, SP, Left Front, INTACH, Conservation Action Trust</t>
+  </si>
+  <si>
+    <t>Obstructionist groups, backed politically by opposition parties, weaponized Public Interest Litigations (PILs) to legally stall the project:
+The Master Challenge (Rajeev Suri v. Union of India): Petitions filed in the Supreme Court alleging procedural impropriety, lack of public consultation, flawed land-use alterations, and questionable environmental clearances in an attempt to quash the master plan entirely.
+The Pandemic Injunction Pleas (May 2021): PILs filed by litigants in the Delhi High Court demanding an immediate stay on construction, disingenuously labeling vital national infrastructure work as a "super-spreader event" and a "vanity project" despite workers being housed on-site under strict bio-bubbles.
+Heritage &amp; Environmental Petitions: Serial challenges before the National Green Tribunal (NGT) and Heritage Conservation Committee seeking stays against tree transplantation, structural demolition of outdated barracks, and plot reclassifications.</t>
+  </si>
+  <si>
+    <t>Supreme Court Clearance (January 5, 2021): In a decisive 2:1 verdict, the Supreme Court cleared the project across all parameters, confirming that environmental, heritage, and land-use approvals were conducted strictly by the book.Delhi High Court Dismissal &amp; Sanction (May 31, 2021): The Delhi High Court dismissed pleas to halt construction, declared Central Vista an "essential and vital project of national importance," and slapped a punitive ₹1,00,000 fine on the petitioners for filing a politically motivated, non-genuine PIL.   Dedication &amp; Deployment: The Kartavya Path was completed and inaugurated in September 2022, followed by the formal dedication of the New Parliament House on May 28, 2023. Construction of the Common Central Secretariat complex (including Kartavya Bhawan) moved forward to consolidate governance.</t>
+  </si>
+  <si>
+    <t>Relentless courtroom maneuvers, stay applications, and administrative obstruction created months of legal friction and operational re-sequencing during 2020–2021. Political boycotts and coordinated legal delays forced the execution machinery to alter logistics, defend basic clearances, and deploy round-the-clock shifts to offset lost project time.</t>
+  </si>
+  <si>
+    <t>The coordinated campaigns by the Congress, the Left parties, and their INDI alliance allies to freeze the Central Vista project were an irresponsible assault on India’s national security and strategic posture. India confronts an aggressive, revisionist China along the Line of Actual Control (LAC), engaged in massive civil-military fusion and rapid construction of fortified command bunkers, electronic warfare bases, and hardened data grids. While Beijing modernized its central power apparatus to react within minutes to strategic contingencies, India's executive leadership, intelligence apparatus, Ministry of Defence, and External Affairs were kept physically fragmented across insecure, fire-prone, 80-year-old structures vulnerable to foreign digital surveillance and espionage.
+Deliberately stalling the integration of a consolidated Common Central Secretariat jeopardized command-and-control efficiency at the height of external military standoffs like the Galwan crisis. Dispersed command nodes cause critical delays in secure document processing, emergency cabinet decisions, and inter-agency coordination. Every frivolous petition dragged through the courts burned hundreds of crores of taxpayer money on inflated commercial rents and compromised strategic response times. Sabotaging India's security and legislative infrastructure to score narrow political points directly undermined the nation's deterrence posture against adversaries like China.</t>
+  </si>
+  <si>
+    <t>https://www.pib.gov.in/PressNoteDetails.aspx?NoteId=154974&amp;ModuleId=3&amp;reg=48&amp;lang=2</t>
+  </si>
+  <si>
+    <t>https://bnblegal.com/news/central-vista-project-vital-and-essential-delhi-hc-rejects-plea-slaps-rs-1-lakh-fine/</t>
+  </si>
+  <si>
+    <t>https://www.scobserver.in/journal/sc-judgment-review-2021-judicial-deference-rajeev-suri-central-vista/</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/india-news/congress-is-frustrated-with-central-vista-because-anurag-thakur-s-jibe-at-opposition-101622818632127.html</t>
   </si>
 </sst>
 </file>
@@ -305,20 +313,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L5" totalsRowShown="0" headerRowDxfId="13" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L5" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:L5" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{36410997-4BAE-4139-BA6C-527DB552268B}" name="Year" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{E6F29A25-DDFD-4825-AAC7-F4F393B282DE}" name="What Initiative" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{FC6EDA76-91BD-41CF-BA1A-F559DA8F7815}" name="Why important for India" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2C020917-0F98-45B5-905B-1CF6B85856B3}" name="Who opposed" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{4124BA6B-A9E0-4092-9991-AE59FA5989C7}" name="Legal Challenges" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{BDB39F99-DE0B-4523-A548-2A645A554516}" name="Final Outcome" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{F9B78EE8-348E-4FB9-9FA7-77D6D17BD91E}" name="Delay" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{9A74D448-6A12-4E1F-AAED-EED2A8412196}" name="Effect on India for the delay" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{0B6BDD86-4352-409C-8807-1DFFC191C171}" name="Proof Link 1" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{84482292-4354-4C6A-9532-D5ACD558D52A}" name="Proof Link 2" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{4DDA3310-D2AD-4926-B2AC-58F7C233DBFE}" name="Proof Link 3" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{36410997-4BAE-4139-BA6C-527DB552268B}" name="Year" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E6F29A25-DDFD-4825-AAC7-F4F393B282DE}" name="What Initiative" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{FC6EDA76-91BD-41CF-BA1A-F559DA8F7815}" name="Why important for India" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{2C020917-0F98-45B5-905B-1CF6B85856B3}" name="Who opposed" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{4124BA6B-A9E0-4092-9991-AE59FA5989C7}" name="Legal Challenges" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{BDB39F99-DE0B-4523-A548-2A645A554516}" name="Final Outcome" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{F9B78EE8-348E-4FB9-9FA7-77D6D17BD91E}" name="Delay" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{9A74D448-6A12-4E1F-AAED-EED2A8412196}" name="Effect on India for the delay" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{0B6BDD86-4352-409C-8807-1DFFC191C171}" name="Proof Link 1" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{84482292-4354-4C6A-9532-D5ACD558D52A}" name="Proof Link 2" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{4DDA3310-D2AD-4926-B2AC-58F7C233DBFE}" name="Proof Link 3" dataDxfId="1"/>
     <tableColumn id="14" xr3:uid="{E31C191E-1D44-46E1-9290-2A81D8E12E6B}" name="Proof Link 4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -616,7 +624,7 @@
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="32" style="1" customWidth="1"/>
     <col min="3" max="3" width="85.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -639,7 +647,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -660,81 +668,83 @@
         <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3" spans="1:12" ht="405" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2019</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -742,37 +752,37 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="375" x14ac:dyDescent="0.25">
@@ -780,34 +790,34 @@
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -824,10 +834,14 @@
     <hyperlink ref="I5" r:id="rId9" xr:uid="{E2C8669E-DD8D-4A51-8D15-D96255441B18}"/>
     <hyperlink ref="J5" r:id="rId10" xr:uid="{83BA019D-EA6C-4D87-8F69-1252DAABDB5A}"/>
     <hyperlink ref="K5" r:id="rId11" xr:uid="{B1805763-2E1D-42D9-ADCF-E25B4A02451E}"/>
+    <hyperlink ref="L2" r:id="rId12" xr:uid="{869838BC-C3E3-45CD-B30E-81BED2D3933C}"/>
+    <hyperlink ref="K2" r:id="rId13" xr:uid="{BD85F19F-41C3-4AD6-A213-E870C7A32A47}"/>
+    <hyperlink ref="J2" r:id="rId14" xr:uid="{1BFE7085-12C3-4CBA-B944-21FEFC85C2BF}"/>
+    <hyperlink ref="I2" r:id="rId15" xr:uid="{5DAC2B73-C720-4395-A8CA-A8ADA64F28E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/India_300_National_Initiatives_History_2_2.xlsx
+++ b/data/India_300_National_Initiatives_History_2_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE372CD-3CB1-4F7F-9107-8506A0B67896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FA266B-66CF-48C2-BAC5-5D034B94FAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -163,29 +163,6 @@
     <t>https://www.thehindu.com/news/national/centre-moves-supreme-court-to-stay-hearings-on-great-nicobar-project/article71525280.ece</t>
   </si>
   <si>
-    <t>The Central Vista Redevelopment is a vital assertion of India’s sovereign state capacity, democratic dignity, and strategic modernization. For nearly a century, the republic operated out of colonial-era structures commissioned in the 1920s under imperial rule—relics designed for an imperial council rather than an assertive, nuclear-armed democracy representing 1.4 billion citizens. The old Parliament suffered from severe architectural fatigue, non-compliance with seismic Zone IV and V safety norms, critical fire vulnerabilities, and cramped legislative chambers incapable of accommodating future democratic representation following delimitation.
-Administratively, executive governance was crippled by being scattered across more than 47 dilapidated buildings and temporary World War II barracks. This fragmentation cost the national exchequer upwards of ₹1,000 crore annually in rental leases, wasteful inter-ministerial physical transit, and logistical bottlenecks. The new development eliminates these operational inefficiencies by establishing a consolidated, subterranean-linked administrative core. It integrates cutting-edge cryptographic and paperless digital infrastructure, fortified physical command centers, and green-certified energy designs, shedding the legacy of colonial subservience and equipping the Indian state to govern with the speed, synergy, and authority demanded of a 21st-century global power.</t>
-  </si>
-  <si>
-    <t>Indian National Congress, CPI(M), CPI, AAP, TMC, DMK, SP, Left Front, INTACH, Conservation Action Trust</t>
-  </si>
-  <si>
-    <t>Obstructionist groups, backed politically by opposition parties, weaponized Public Interest Litigations (PILs) to legally stall the project:
-The Master Challenge (Rajeev Suri v. Union of India): Petitions filed in the Supreme Court alleging procedural impropriety, lack of public consultation, flawed land-use alterations, and questionable environmental clearances in an attempt to quash the master plan entirely.
-The Pandemic Injunction Pleas (May 2021): PILs filed by litigants in the Delhi High Court demanding an immediate stay on construction, disingenuously labeling vital national infrastructure work as a "super-spreader event" and a "vanity project" despite workers being housed on-site under strict bio-bubbles.
-Heritage &amp; Environmental Petitions: Serial challenges before the National Green Tribunal (NGT) and Heritage Conservation Committee seeking stays against tree transplantation, structural demolition of outdated barracks, and plot reclassifications.</t>
-  </si>
-  <si>
-    <t>Supreme Court Clearance (January 5, 2021): In a decisive 2:1 verdict, the Supreme Court cleared the project across all parameters, confirming that environmental, heritage, and land-use approvals were conducted strictly by the book.Delhi High Court Dismissal &amp; Sanction (May 31, 2021): The Delhi High Court dismissed pleas to halt construction, declared Central Vista an "essential and vital project of national importance," and slapped a punitive ₹1,00,000 fine on the petitioners for filing a politically motivated, non-genuine PIL.   Dedication &amp; Deployment: The Kartavya Path was completed and inaugurated in September 2022, followed by the formal dedication of the New Parliament House on May 28, 2023. Construction of the Common Central Secretariat complex (including Kartavya Bhawan) moved forward to consolidate governance.</t>
-  </si>
-  <si>
-    <t>Relentless courtroom maneuvers, stay applications, and administrative obstruction created months of legal friction and operational re-sequencing during 2020–2021. Political boycotts and coordinated legal delays forced the execution machinery to alter logistics, defend basic clearances, and deploy round-the-clock shifts to offset lost project time.</t>
-  </si>
-  <si>
-    <t>The coordinated campaigns by the Congress, the Left parties, and their INDI alliance allies to freeze the Central Vista project were an irresponsible assault on India’s national security and strategic posture. India confronts an aggressive, revisionist China along the Line of Actual Control (LAC), engaged in massive civil-military fusion and rapid construction of fortified command bunkers, electronic warfare bases, and hardened data grids. While Beijing modernized its central power apparatus to react within minutes to strategic contingencies, India's executive leadership, intelligence apparatus, Ministry of Defence, and External Affairs were kept physically fragmented across insecure, fire-prone, 80-year-old structures vulnerable to foreign digital surveillance and espionage.
-Deliberately stalling the integration of a consolidated Common Central Secretariat jeopardized command-and-control efficiency at the height of external military standoffs like the Galwan crisis. Dispersed command nodes cause critical delays in secure document processing, emergency cabinet decisions, and inter-agency coordination. Every frivolous petition dragged through the courts burned hundreds of crores of taxpayer money on inflated commercial rents and compromised strategic response times. Sabotaging India's security and legislative infrastructure to score narrow political points directly undermined the nation's deterrence posture against adversaries like China.</t>
-  </si>
-  <si>
     <t>https://www.pib.gov.in/PressNoteDetails.aspx?NoteId=154974&amp;ModuleId=3&amp;reg=48&amp;lang=2</t>
   </si>
   <si>
@@ -196,6 +173,24 @@
   </si>
   <si>
     <t>https://www.hindustantimes.com/india-news/congress-is-frustrated-with-central-vista-because-anurag-thakur-s-jibe-at-opposition-101622818632127.html</t>
+  </si>
+  <si>
+    <t>It shatters colonial chains, replacing outdated, earthquake-vulnerable British barracks with an indigenous architectural marvel. It unites fragmented ministries to slash wasteful annual office rents of ₹1,000 crore, modernizes national governance infrastructure for centuries to come, and delivers expanded legislative chambers ready for future delimitation. It stands as an unapologetic, world-class monument to India’s sovereign democratic power and civilizational pride.</t>
+  </si>
+  <si>
+    <t>Opponents filed multiple PILs in the Supreme Court and Delhi High Court, weaponizing environmental clearances, land-use modifications, heritage conservation laws, and the pandemic to secure an injunction and paralyze construction.</t>
+  </si>
+  <si>
+    <t>A resounding victory for national progress: the Supreme Court crushed obstructive pleas, upheld all clearances, and the New Parliament was officially inaugurated and made fully operational.</t>
+  </si>
+  <si>
+    <t>Relentless PILs, weaponized petitions, and politically motivated boycott campaigns caused procedural friction and delayed construction milestones by several months beyond original targets.</t>
+  </si>
+  <si>
+    <t>The deliberate sabotage engineered by the Congress, Left parties, and their allied ecosystem inflicted severe harm on India’s momentum. By dragging a critical national infrastructure project through legal quagmires, these obstructionist elements directly bled public funds, forced the exchequer to waste thousands of crores on dilapidated rented offices, and paralyzed administrative synergy. Their agenda sought to keep Indian democracy trapped inside decrepit, unsafe colonial relics just to score petty political points. Stalling the heart of Indian governance during critical years exposed their sheer hostility toward India shedding its subservient colonial baggage and asserting itself on the global stage.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, AAP, DMK, RJD, SP, NCP, Shiv Sena (UBT), activist NGOs, Pseudo-Environmentalist Lobbies</t>
   </si>
 </sst>
 </file>
@@ -671,7 +666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="285" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -679,34 +674,34 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="405" x14ac:dyDescent="0.25">

--- a/data/India_300_National_Initiatives_History_2_2.xlsx
+++ b/data/India_300_National_Initiatives_History_2_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FA266B-66CF-48C2-BAC5-5D034B94FAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D60D92-86BC-40D3-BECA-41DB06F8F98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Year</t>
   </si>
@@ -61,26 +61,9 @@
     <t>Abrogation of Article 370 and Reorganisation of Jammu &amp; Kashmir</t>
   </si>
   <si>
-    <t>The abrogation of Article 370 was a monumental, historic, and absolutely essential masterstroke for the complete and total integration of India. For seven decades, this constitutional anomaly acted as a psychological and legal barrier, preventing the true unification of Jammu and Kashmir with the rest of the motherland. Eradicating this flawed provision was crucial for national security, as it effectively dismantled the ecosystem of separatism that anti-India forces and neighboring adversaries exploited for decades. By revoking the special status, the Indian government decisively crushed the insidious narrative of a "separate identity" that fueled terrorism and unrest. It brought all citizens of Jammu and Kashmir under the umbrella of the Indian Constitution, guaranteeing them the exact same fundamental rights, liberties, and developmental opportunities enjoyed by every other Indian.
-This initiative was profoundly important for ensuring gender justice and social equality, as the discriminatory Article 35A (which derived its power from Article 370) was inherently prejudiced against women, Dalits, and marginalized communities. By scrapping it, India ensured that historically oppressed groups, such as the Valmiki community and West Pakistani refugees, finally received voting rights and equal citizenship. Economically, removing the barrier opened the floodgates for nationwide investments, infrastructure projects, and industrial growth, paving the way for the youth of Kashmir to embrace prosperity rather than radicalization. The abrogation was not merely a legislative amendment; it was a civilizational course correction. It asserted India's absolute and unquestionable sovereignty over its territory, proving to the world that India will never compromise on its territorial integrity. It stands as a glorious testament to a strong, decisive leadership prioritizing the nation's supreme interests over petty appeasement politics, ultimately securing a unified, peaceful, and prosperous future for the entire nation.</t>
-  </si>
-  <si>
     <t>Legal Challenges</t>
   </si>
   <si>
-    <t>Opponents filed numerous petitions in the Supreme Court, arguing that Article 370 had attained a permanent status after the state's Constituent Assembly dissolved in 1957. They challenged the validity of Presidential Orders (CO 272 and CO 273), arguing that the Union government unconstitutionally bypassed the state legislative assembly by acting while the state was under President's Rule.</t>
-  </si>
-  <si>
-    <t>On December 11, 2023, a five-judge Constitution Bench of the Supreme Court, led by Chief Justice D.Y. Chandrachud, unanimously upheld the abrogation. The Court firmly ruled that Article 370 was always a temporary provision and validated the President's power to revoke it to ensure the state's complete integration into India. The Court also upheld the reorganization of the state into two Union Territories and ordered that legislative assembly elections be conducted by September 2024.</t>
-  </si>
-  <si>
-    <t>Although Article 370 was explicitly drafted in Part XXI of the Constitution under "Temporary, Transitional and Special Provisions," successive governments delayed its removal for 70 years. This delay was primarily driven by a lack of political will, regional vote-bank appeasement, and fears of diplomatic or violent backlash.</t>
-  </si>
-  <si>
-    <t>The catastrophic seventy-year delay in abrogating Article 370 inflicted unimaginable wounds on the Republic of India, costing the nation heavily in blood, resources, and internal security. By allowing a "temporary" provision to fester for decades, previous administrations effectively nurtured a breeding ground for cross-border terrorism, radicalization, and violent separatism. The most devastating consequence was the tragic loss of thousands of brave Indian soldiers, security personnel, and innocent civilians who perished in the relentless proxy war orchestrated by Pakistan. The special status created a legal and psychological vacuum that anti-India syndicates exploited to fund stone-pelting networks, radicalize the youth, and paralyze normal life in the Kashmir valley—incidents of which dropped drastically only after the abrogation.
-Furthermore, the prolonged delay allowed deeply entrenched political dynasties in the region to monopolize power, siphon off massive amounts of central funds, and deny grassroots democratic development to the common Kashmiri. Socially, the delay perpetuated horrific human rights injustices under the guise of autonomy. Generations of women lost their property rights if they married outside the state, and marginalized workers were legally barred from upward mobility. The constitutional isolation severely stunted economic growth, scaring away private investment, industries, and world-class educational institutions, which left the youth unemployed and vulnerable to extremist propaganda. Diplomatically, the lingering ambiguity allowed hostile neighbors to continuously internationalize the Kashmir issue, constantly distracting India's foreign policy focus. Had this cancerous provision been excised decades earlier, India would have been spared decades of bloodshed, severe economic stagnation in the region, and the forced exodus of the Kashmiri Pandit community, vastly accelerating the nation's rise as an unhindered global superpower.</t>
-  </si>
-  <si>
     <t>Proof Link 4</t>
   </si>
   <si>
@@ -96,15 +79,9 @@
     <t>https://www.outlookindia.com/national/in-photos-opposition-parties-protest-on-the-7th-anniversary-of-article-370s-abrogation?photo=1</t>
   </si>
   <si>
-    <t xml:space="preserve">Indian National Congress, Left, DMK, RJD, Trinamool Congress, NCP, National Conference, PDP, Pakistan-backed Separatist </t>
-  </si>
-  <si>
     <t>Citizenship (Amendment) Act, 2019 (CAA)</t>
   </si>
   <si>
-    <t>Congress, Left, TMC, CPI(M), IUML, DMK, AIMIM, AASU, UNHRC</t>
-  </si>
-  <si>
     <t>https://timesofindia.indiatimes.com/india/congress-opposed-caa-due-to-vote-bank-politics-says-amit-shah-in-hyderabad-/articleshow/108431868.cms</t>
   </si>
   <si>
@@ -114,46 +91,12 @@
     <t>https://economictimes.indiatimes.com/news/india/west-bengal-to-investigate-2019-anti-caa-protests-vandalism-and-arson-cases/articleshow/131554934.cms?from=mdr</t>
   </si>
   <si>
-    <t>Proponents of the Citizenship (Amendment) Act argue that the legislation is a vital humanitarian necessity and a direct fulfillment of India’s historical and moral obligations following the partition of 1947. The partition, executed along religious lines, left substantial minority populations—specifically Hindus, Sikhs, Buddhists, Jains, Parsis, and Christians—in the newly formed Islamic republics of Pakistan, and later Bangladesh, as well as in neighboring Afghanistan. Over the decades, these communities have faced well-documented, systemic religious persecution, including forced conversions, discriminatory blasphemy laws, and targeted violence, leading to a drastic decline in their demographic presence in those nations. The Indian government asserts that these historically persecuted minorities have nowhere else to seek refuge but India, aligning with the country's ancient civilizational ethos of providing sanctuary to the oppressed. Supporters point out that international frameworks often recognize the need for tailored solutions for specifically targeted, vulnerable demographic groups. By reducing the mandatory residency requirement for naturalization from eleven years to five years, the CAA provides a dignified, expedited legal pathway for these stateless individuals. Furthermore, supporters emphasize that the Act clearly distinguishes between persecuted refugees seeking asylum for sheer survival and illegal economic immigrants. The government has repeatedly clarified that the legislation does not revoke or dilute the citizenship of any existing Indian citizen, regardless of their religion, but serves solely as a specialized, one-time protective measure to secure the human rights of specific marginalized groups.</t>
-  </si>
-  <si>
-    <t>Over 200 petitions, led primarily by the Indian Union Muslim League (IUML), were filed in the Supreme Court. Challengers sought to halt the initiative, arguing it violates the Constitution's secular fabric—specifically Article 14 (Right to Equality) and Article 21—by making religion a criterion for citizenship and explicitly excluding Muslims.</t>
-  </si>
-  <si>
-    <t>The Supreme Court repeatedly declined to grant an interim stay on the legislation. The Union Government officially notified the CAA rules in March 2024, effectively implementing the law and initiating the process of granting citizenship certificates. The Supreme Court has scheduled final hearings on the constitutional validity of the Act for May 2026.</t>
-  </si>
-  <si>
-    <t>Although Parliament passed the CAA in December 2019, its operational implementation was delayed until March 2024. This delay was attributed to the outbreak of the COVID-19 pandemic, the necessity of drafting detailed operational frameworks to exempt specific tribal and Inner Line Permit (ILP) areas in the Northeast, and the massive nationwide protests that erupted immediately after its passage.</t>
-  </si>
-  <si>
-    <t>The prolonged delay in implementation, coupled with a highly polarized political environment, resulted in a severe period of domestic instability, massive civil unrest, and significant socioeconomic disruption across India. In the aftermath of the Act's passage, widespread protests erupted, which the government and its supporters argue were heavily fueled by misinformation and deliberate provocation from opposition parties aiming to create panic among Indian minorities. Because the rules were not immediately formalized and communicated, a narrative took root that the CAA, combined with a proposed nationwide National Register of Citizens (NRC), would be used to systematically strip Indian Muslims of their citizenship. The government repeatedly clarified that the CAA had no provision to revoke anyone's citizenship, but the delay allowed fearmongering to persist. This prolonged ambiguity provided fertile ground for sustained agitation that quickly escalated into widespread violence and destruction of public infrastructure. During the protests, railway stations, buses, and public property were severely vandalized or set on fire, particularly in states like West Bengal, Uttar Pradesh, and Delhi. The human cost was tragically high, with dozens of fatalities resulting from violent clashes and police firing, including at least 27 deaths in Uttar Pradesh and several in Assam. The prolonged unrest ultimately culminated in the devastating Delhi riots of February 2020, which resulted in over 50 deaths and massive property damage. Furthermore, the civic disruption severely impacted local economies, necessitated extended internet shutdowns in various states, and temporarily strained diplomatic relations with neighboring Bangladesh.</t>
-  </si>
-  <si>
     <t>https://indianexpress.com/elections/showdown-in-bengal-opp-is-spreading-lies-on-caa-giving-citizenship-is-modis-guarantee-pm-9252240/</t>
   </si>
   <si>
     <t>The Great Nicobar Island Development Project</t>
   </si>
   <si>
-    <t>Congress, Left, Trinamool Congress, Conservation Action Trust, environmental NGOs, tribal rights activist groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Nicobar Island Development Project is an absolute necessity and a monumental masterstroke for India’s long-term economic prosperity and strategic sovereignty. Geographically, Great Nicobar is a priceless national asset situated a mere 150 kilometers from the Strait of Malacca, one of the world's most critical and busiest maritime chokepoints where a vast majority of global trade transits. For decades, India has inexplicably neglected this geographical goldmine, relying heavily on foreign transshipment hubs like Colombo, Klang, and Singapore. This reliance drains vital foreign exchange, increases logistics costs, and leaves Indian supply chains vulnerable. This visionary project fundamentally changes the paradigm. By building a massive, state-of-the-art transshipment terminal in our own sovereign territory, India will aggressively capture international gateway cargo, transforming the nation into an unstoppable global maritime and economic powerhouse.   Furthermore, this initiative is the ultimate catalyst for India's "Blue Economy" and the "Act East Policy," seamlessly connecting the Indian mainland to Southeast Asia. Establishing a robust, self-sustaining military and civilian ecosystem on Great Nicobar guarantees that the Andaman and Nicobar Command—India’s only tri-service command—can operate with unmatched efficiency, enhanced surveillance, and superior naval logistics. The meticulously planned township and renewable energy installations will foster unprecedented regional development, creating immense employment opportunities while prioritizing ecological balance through strict mitigations like compensatory afforestation. Opposing this project means opposing India’s rightful emergence as a dominant, self-reliant superpower on the global stage. It is an extraordinary, future-defining initiative that must be completed without any hesitation. </t>
-  </si>
-  <si>
-    <t>Petitions were filed before the National Green Tribunal (NGT) and the Calcutta High Court to halt the project entirely. Opponents challenged the statutory environmental and forest clearances, citing alleged Coastal Regulation Zone (ICRZ-IA) violations, threats to biodiversity (such as the Giant Leatherback Turtle), deforestation concerns, and alleged inadequate impact assessments regarding the indigenous Shompen and Nicobarese tribal communities.</t>
-  </si>
-  <si>
-    <t>In February 2026, the NGT ruled decisively in favor of the project, concluding that there was no need to interfere with the environmental clearance, citing the implementation of adequate safeguards and the overriding strategic importance of the project. To prevent further judicial roadblocks in lower courts, the Centre moved the Supreme Court in September 2026 to stay ongoing proceedings in the High Court, clearing the path for execution.</t>
-  </si>
-  <si>
-    <t>The project has faced considerable delays due to relentless environmental litigation, stays sought by activists in multiple courts, the formation of investigative High-Powered Committees (HPC), and politically motivated resistance questioning the clearance procedures.</t>
-  </si>
-  <si>
-    <t>The persistent and calculated attempts to delay or stop the Great Nicobar Development Project border on strategic sabotage, severely compromising India's national security architecture at a highly volatile time. Every single day this project is delayed is a direct geopolitical victory for China. Beijing has been relentlessly expanding its footprint in the Indian Ocean, securing military and port access in Sri Lanka, Pakistan, and Djibouti as part of its aggressive "String of Pearls" strategy. China frequently deploys submarines and surveillance vessels in these waters, actively seeking to dominate the very sea lanes that India relies on for its energy and trade security. By stalling the construction of the Great Nicobar military-civil airport and the naval bases, opponents are effectively blinding India’s maritime watchtower.
-Great Nicobar Island provides a supreme tactical advantage to monitor the Six Degree Channel and the Malacca Strait. Halting this infrastructure means the Andaman and Nicobar Command is deprived of critical logistical support, advanced surveillance capabilities, and rapid deployment readiness. Delaying this project severely weakens India’s ability to counter maritime piracy, terrorism, and undue Chinese dominance in our own strategic backyard. While activists hyper-fixate on bureaucratic environmental hurdles, they ignore the existential threat of a hostile neighbor heavily militarizing the Indian Ocean Region. A paralyzed project means India loses crucial time in solidifying its defense perimeter. Stopping this initiative is an unforgivable blunder that actively endangers India’s sovereign borders, neutralizes our strategic leverage against China, and leaves our maritime frontiers dangerously vulnerable to extra-regional aggression.</t>
-  </si>
-  <si>
     <t>https://www.indiatoday.in/india-today-insight/story/how-great-nicobar-is-emerging-as-indias-strategic-answer-to-chinas-maritime-reach-2910697-2026-05-12</t>
   </si>
   <si>
@@ -191,6 +134,95 @@
   </si>
   <si>
     <t>Congress, CPI(M), CPI, TMC, AAP, DMK, RJD, SP, NCP, Shiv Sena (UBT), activist NGOs, Pseudo-Environmentalist Lobbies</t>
+  </si>
+  <si>
+    <t>It obliterated a toxic relic of partition and realized the sacred vision of "Ek Vidhan, Ek Nishan, Ek Pradhan." Article 370 was an artificial constitutional barricade that bred cross-border separatism, shielded terror networks, and robbed women, Dalits, and marginalized communities of core constitutional protections like reservations and equal property rights. By smashing this discriminatory wall, India fully integrated Jammu &amp; Kashmir into the Union, crushing decades of dynastic loot and anti-national blackmail. It unleashed grass-roots democracy via Panchayati Raj, triggered record investments, tourism, and infrastructure growth, and restored sovereign authority over the nation's crown jewel. The abrogation permanently cemented Bharat's territorial integrity and proved that India will never compromise on its sovereignty.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, NC, PDP, TMC, DMK, AAP, SP, RJD, People's Union for Civil Liberties, activist NGOs</t>
+  </si>
+  <si>
+    <t>Over twenty-three petitions were filed by opposition politicians, separatist sympathizers, and activist outfits in the Supreme Court, desperately challenging Presidential Orders CO 272 and CO 273, the exercise of powers under President’s Rule, and the state's bifurcation. They falsely argued that Article 370 had acquired permanent status, attempting to stall national integration through protracted constitutional litigation.</t>
+  </si>
+  <si>
+    <t>A monumental victory for India's sovereignty: on December 11, 2023, a five-judge Constitution Bench of the Supreme Court unanimously upheld the abrogation as constitutionally valid. The apex court ruled that Article 370 was purely a temporary, transitional provision, established that Jammu and Kashmir held no internal sovereignty, and validated the constitutional exercise of power by the Union.</t>
+  </si>
+  <si>
+    <t>Opposition parties and activist lawyers dragged the challenge through years of deliberate legal maneuvers, keeping petitions lingering from August 2019 until December 2023. Their desperate push to secure stay orders and prolong judicial limbo aimed to spark international friction, paralyze administrative reforms, and stall decisive governance on the ground.</t>
+  </si>
+  <si>
+    <t>The obstinate resistance mounted by Congress, the Left parties, and their INDI alliance ecosystem inflicted severe harm on national security, social justice, and democratic integration. For over seven decades, this regressive political syndicate nurtured a temporary provision to appease regional dynasts, deliberately pampering secessionist cliques while shielding terror conduits, stone-pelting cartels, and cross-border handlers. When Parliament decisively eliminated this historical blunder, these obstructionists rushed to the courts to reverse the will of the nation.   By fighting to prolong constitutional uncertainty, these parties actively undermined the morale of frontline security forces, provided fodder to hostile foreign propaganda, and stalled the socio-economic empowerment of millions of Valmikis, Gorkhas, West Pakistan refugees, and local women who had been disenfranchised for generations. Their obstructionism exposed a sheer willingness to compromise national sovereignty and leave Jammu and Kashmir simmering in instability purely to protect communal vote banks and preserve elite dynastic monopolies.</t>
+  </si>
+  <si>
+    <t>The Citizenship (Amendment) Act is an act of civilizational justice and a sacred humanitarian pledge fulfilled. For decades, millions of persecuted minorities—Hindus, Sikhs, Buddhists, Jains, Parsis, and Christians—endured forced conversions, abductions, and systemic terror in Pakistan, Bangladesh, and Afghanistan, fleeing to India as broken, stateless refugees. CAA rescues them from humiliating legal limbo, granting legitimate citizenship, dignity, property rights, and fundamental constitutional protections. It does not take away a single Indian citizen’s rights; it merely extends a protective sanctuary to victims of brutal religious apartheid. By asserting its civilizational duty, sovereign India demonstrated that it will never abandon the victims of partition-era tragedies to brutal fundamentalist regimes.</t>
+  </si>
+  <si>
+    <t>Over 200 petitions were filed in the Supreme Court by opposition leaders, radical outfits, and activist lawyers. They weaponized Article 14, peddled bogus claims of religious discrimination, and filed serial stay applications to paralyze the law and block rule notification.</t>
+  </si>
+  <si>
+    <t>Congress, TMC, CPI(M), CPI, AAP, DMK, SP, RJD, AIMIM, IUML, left-leaning student groups, foreign-funded activist NGOs</t>
+  </si>
+  <si>
+    <t>National sovereignty and humanitarian resolve prevailed: the Supreme Court repeatedly refused to stay the Act or its rules. The Union Government notified the CAA Rules, operationalized fast-track digital portals, and began issuing citizenship certificates across India.</t>
+  </si>
+  <si>
+    <t>Violent, orchestrated street agitations, toxic disinformation campaigns, and endless procedural litigations by opposition parties stalled rule-framing and implementation for over four years, deferring life-saving legal relief from 2019 until 2024.</t>
+  </si>
+  <si>
+    <t>The deliberate sabotage engineered by Congress, the Left parties, and their INDI alliance ecosystem inflicted untold human misery and severe reputational damage on India. For over four years, persecuted refugees—most notably marginalized Dalit communities like the Matuas and Namasudras—were forced to languish in squalor without identity cards, formal jobs, education, or basic healthcare, purely because the opposition weaponized their suffering for cynical vote-bank mathematics.
+Worse still, these parties actively incited communal panic, sponsored highway blockades, and stoked street riots by lying that Indian citizens would lose their citizenship. They peddled hostile narratives to foreign lobbies, internationalizing India’s domestic humanitarian law and tarnishing the country's global standing. Sacrificing the dignity of persecuted minorities to appease radical vote banks exposed the opposition's complete moral bankruptcy and contempt for India's civilizational obligations.</t>
+  </si>
+  <si>
+    <t>It is India’s non-negotiable maritime fortress and an unsinkable aircraft carrier guarding the entrance to the Malacca Strait. Dominating the Six Degree Channel—where global energy arteries pass—it decisively smashes China’s belligerent "String of Pearls" encirclement and counters hostile PLAN submarine aggression. Integrating an International Container Transhipment Port at Galathea Bay, a joint civil-military dual-use international air base, and power infrastructure, it turns the Andaman &amp; Nicobar Tri-Services Command into an unbreachable maritime sentinel. Economically, it frees Indian trade from humiliating dependence on foreign transhipment hubs like Colombo and Singapore, retaining billions of dollars in sovereign revenue.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, DMK, AAP, activist NGOs, foreign-funded green lobbies</t>
+  </si>
+  <si>
+    <t>Obstructionist petitions were filed before the National Green Tribunal, Calcutta High Court, and Supreme Court. Opponents weaponized Coastal Regulation Zone norms, biological diversity concerns, and Forest Rights Act disputes to demand blanket stays, aiming to completely paralyze vital military-civilian construction.</t>
+  </si>
+  <si>
+    <t>National security prevailed: the National Green Tribunal upheld the environmental clearances, and the Supreme Court repeatedly refused to stay the project, acknowledging its overriding strategic imperatives while ensuring high-powered oversight committees enforce strict statutory safeguards.</t>
+  </si>
+  <si>
+    <t>Relentless opposition petitions, procedural litigation, and coordinated international misinformation campaigns caused persistent regulatory drag, procedural scrutiny delays, and multi-year bureaucratic roadblocks, slowing rapid ground fortification.</t>
+  </si>
+  <si>
+    <t>Every single second lost on the Great Nicobar Project plays directly into the hands of hostile foreign adversaries, most notably China. The Congress, the Left parties, and their INDI alliance ecosystem have displayed unforgivable recklessness by attempting to derail India’s most critical geopolitical outpost. While the Chinese navy aggressively ramps up militarized port facilities across Djibouti, Gwadar, and Hambantota, and conducts invasive spy ship operations across the Indian Ocean, these regressive domestic forces fought tooth and nail in courts to keep India’s front line unarmed and vulnerable.
+Sabotaging this initiative leaves India’s southern maritime flank exposed, starves the Tri-Services Command of rapid surveillance staging capabilities, and perpetuates the bleeding of hundreds of millions of dollars in port revenues to foreign hands. Sacrificing sovereign territorial defense and maritime dominance at the altar of cynical political obstructionism borders on treasonous negligence against Mother India’s security architecture.</t>
+  </si>
+  <si>
+    <t>Narmada Dam (Sardar Sarovar Project)</t>
+  </si>
+  <si>
+    <t>It is the unshakeable lifeline of Western India and a cornerstone of national security, food sovereignty, and economic survival. By taming the Narmada, it eradicated parched, drought-ridden desperation across Saurashtra, Kutch, and arid belts of Rajasthan, channeling life-saving drinking water directly to forward defense deployments and BSF border outposts along the hostile Indo-Pak frontier. Generating 1,450 MW of clean hydroelectric power and irrigating over 18 lakh hectares of barren land, it transformed chronic famine zones into agricultural powerhouses. It insulated critical border populations from destabilizing water crises, permanently securing national resource resilience.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, Left Front, Narmada Bachao Andolan, foreign-funded activist NGOs, pseudo-environmentalist lobbies,</t>
+  </si>
+  <si>
+    <t>Opponents and activist networks dragged the project into the Supreme Court and international tribunals, weaponizing PILs to allege human rights abuses, rehabilitation inadequacies, and seismic hazards. They secured an injunction that halted construction between 1995 and 1999, attempting to permanently freeze work.</t>
+  </si>
+  <si>
+    <t>National sovereignty and judicial realism crushed ideological obstructionism: on October 18, 2000, the Supreme Court permitted construction in phased increments. In 2014, the final clearance raised the dam to its full 138.68-meter height, culminating in its 2017 national dedication.</t>
+  </si>
+  <si>
+    <t>Paralyzed by bureaucratic paralysis under successive Congress regimes, PIL warfare, and foreign-funded NGO lobbying, the project was deliberately choked for nearly four decades beyond initial timelines.</t>
+  </si>
+  <si>
+    <t>The deliberate sabotage engineered by the Congress, the Left parties, and their activist ecosystem inflicted catastrophic wounds on India’s national security and economy. By halting construction for years, these obstructionists starved millions of farmers of irrigation, triggered devastating droughts across Gujarat and Rajasthan, and forced border states into profound agrarian and economic distress. Most egregiously, denying water to strategic border regions like Kutch severely jeopardized military logistics and the living conditions of frontline Border Security Force personnel defending sensitive international borders.   Public funds bled as costs skyrocketed by thousands of crores due to inflation, while precious freshwater washed unused into the sea every monsoon. The opposition cabal weaponized international pressure and engineered the withdrawal of World Bank funding to keep India energy-deficient and food-insecure. Sacrificing border security, farmer welfare, and national hydration at the altar of anti-development ideology remains one of the most disgraceful betrayals of India's strategic interests.</t>
+  </si>
+  <si>
+    <t>https://indiankanoon.org/doc/1938608/</t>
+  </si>
+  <si>
+    <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=1503211&amp;reg=48&amp;lang=2</t>
+  </si>
+  <si>
+    <t>https://demo.ssnnl.in/components-of-project.aspx</t>
+  </si>
+  <si>
+    <t>https://indianexpress.com/article/explained/bjp-congress-medha-patkar-role-in-narmada-bachao-andolan-8281349/</t>
   </si>
 </sst>
 </file>
@@ -308,8 +340,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L5" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L5" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L6" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L6">
+    <sortCondition ref="A1:A6"/>
+  </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{36410997-4BAE-4139-BA6C-527DB552268B}" name="Year" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{E6F29A25-DDFD-4825-AAC7-F4F393B282DE}" name="What Initiative" dataDxfId="10"/>
@@ -613,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B667CDE-8E2B-439F-AECC-B04A1264504F}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -642,7 +677,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -663,48 +698,48 @@
         <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="285" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
+    <row r="2" spans="1:12" ht="270" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1961</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="405" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2019</v>
       </c>
@@ -712,109 +747,147 @@
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="4" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="330" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="375" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="330" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="285" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="2"/>
+      <c r="I6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -829,14 +902,18 @@
     <hyperlink ref="I5" r:id="rId9" xr:uid="{E2C8669E-DD8D-4A51-8D15-D96255441B18}"/>
     <hyperlink ref="J5" r:id="rId10" xr:uid="{83BA019D-EA6C-4D87-8F69-1252DAABDB5A}"/>
     <hyperlink ref="K5" r:id="rId11" xr:uid="{B1805763-2E1D-42D9-ADCF-E25B4A02451E}"/>
-    <hyperlink ref="L2" r:id="rId12" xr:uid="{869838BC-C3E3-45CD-B30E-81BED2D3933C}"/>
-    <hyperlink ref="K2" r:id="rId13" xr:uid="{BD85F19F-41C3-4AD6-A213-E870C7A32A47}"/>
-    <hyperlink ref="J2" r:id="rId14" xr:uid="{1BFE7085-12C3-4CBA-B944-21FEFC85C2BF}"/>
-    <hyperlink ref="I2" r:id="rId15" xr:uid="{5DAC2B73-C720-4395-A8CA-A8ADA64F28E1}"/>
+    <hyperlink ref="L6" r:id="rId12" xr:uid="{869838BC-C3E3-45CD-B30E-81BED2D3933C}"/>
+    <hyperlink ref="K6" r:id="rId13" xr:uid="{BD85F19F-41C3-4AD6-A213-E870C7A32A47}"/>
+    <hyperlink ref="J6" r:id="rId14" xr:uid="{1BFE7085-12C3-4CBA-B944-21FEFC85C2BF}"/>
+    <hyperlink ref="I6" r:id="rId15" xr:uid="{5DAC2B73-C720-4395-A8CA-A8ADA64F28E1}"/>
+    <hyperlink ref="K2" r:id="rId16" xr:uid="{6E753CA4-545C-44D7-96F1-5BB67BA545B2}"/>
+    <hyperlink ref="L2" r:id="rId17" xr:uid="{2998BFA7-0E72-421E-B188-FC558D33BFF9}"/>
+    <hyperlink ref="J2" r:id="rId18" xr:uid="{D3AD9D0E-8F7C-4AA3-AEB3-B998249D1FFE}"/>
+    <hyperlink ref="I2" r:id="rId19" xr:uid="{F989E7E7-D239-4F06-B64F-7D54481F0111}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/India_300_National_Initiatives_History_2_2.xlsx
+++ b/data/India_300_National_Initiatives_History_2_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D60D92-86BC-40D3-BECA-41DB06F8F98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6AA440-0A65-474E-9524-22812B7790A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>Year</t>
   </si>
@@ -223,6 +223,39 @@
   </si>
   <si>
     <t>https://indianexpress.com/article/explained/bjp-congress-medha-patkar-role-in-narmada-bachao-andolan-8281349/</t>
+  </si>
+  <si>
+    <t>Pokhran Nuclear Test</t>
+  </si>
+  <si>
+    <t>It is the non-negotiable bedrock of India’s national security, strategic autonomy, and sovereign survival. Flanked by two colluding, hostile nuclear-armed adversaries—an expansionist China and an export hub of cross-border jihad in Pakistan—India faced an existential security dilemma. The Pokhran tests obliterated hypocritical global nuclear apartheid, smashed the discriminatory non-proliferation monopoly of the P-5 powers, and erected an impenetrable shield of credible strategic deterrence.   Operation Shakti liberated India from decades of foreign intimidation and atomic blackmail. It validated thermonuclear, fission, and sub-kiloton weapon designs, directly birthing an unassailable strategic nuclear triad across land, air, and sea. Anchored by the doctrine of Credible Minimum Deterrence and No First Use, it ensured that no hostile power can ever contemplate waging war against Indian soil without facing guaranteed, catastrophic retaliation. It established that the defense of 1.4 billion citizens will never be mortgaged to foreign capitals.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, Left Front, Samajwadi Party, Movement in India for Nuclear Disarmament, foreign-funded anti-nuclear activist NGOs</t>
+  </si>
+  <si>
+    <t>Discriminatory global treaties—the Nuclear Non-Proliferation Treaty (NPT) and the Comprehensive Nuclear-Test-Ban Treaty (CTBT)—were weaponized internationally to encircle and legally suffocate India’s indigenous nuclear deterrent. Major powers triggered automatic punitive statutes, notably the US Glenn and Symington Amendments, slapping blanket economic and high-technology export embargoes. Simultaneously, United Nations Security Council Resolution 1172 was enacted to legally coerce India into rolling back its nuclear weapons programme, halting missile delivery development, and surrendering its sovereign strategic defense.</t>
+  </si>
+  <si>
+    <t>National sovereignty and iron political resolve triumphed over global coercion. India conducted five consecutive underground nuclear detonations, proving complete thermonuclear weaponization. Prime Minister Atal Bihari Vajpayee officially declared India a full-fledged nuclear weapons state. India withstood crippling multilateral sanctions, forced world powers to recognize its de facto nuclear status, integrated fully into global civil nuclear commerce via NSG waivers, and established an unshakeable land-air-sea strategic triad.</t>
+  </si>
+  <si>
+    <t>A debilitating 24-year vacuum ensued after the 1974 test due to chronic political indecision, Western intimidation, and lack of geopolitical resolve. Most egregiously, in late 1995, advanced preparations for tests were abruptly surrendered when the Narasimha Rao government buckled under American diplomatic pressure after CIA spy satellites detected movement in the Thar Desert. Spineless leadership repeatedly postponed weaponization, leaving the armed forces strategically exposed until May 1998.</t>
+  </si>
+  <si>
+    <t>The criminal 24-year delay between 1974 and 1998, followed by the venomous opposition to Operation Shakti, was an unforgivable betrayal of India’s national security by the Congress, the Left parties, and their allied ecosystem. For nearly a quarter-century, while China built an enormous atomic arsenal and actively proliferated nuclear weapon blueprints and M-11 ballistic missiles to Pakistan, spineless ruling establishments in New Delhi cowered in fear of foreign rebukes. This cowardly hesitation left the Indian military critically vulnerable to a coordinated, two-front nuclear pincer, exposing our frontline soldiers and sovereign territory to brazen blackmail, incursions, and cross-border proxy terror.When Prime Minister Atal Bihari Vajpayee finally demonstrated the civilizational courage to execute Pokhran-II, the Congress, the Left Front, and their INDI alliance satellites responded with sheer domestic sabotage. Instead of celebrating an epochal breakthrough by our scientists, the Left shamefully parroted Beijing’s propaganda, condemned the tests as jingoistic militarism, and disparaged our sovereign security shield as a "Hindu bomb". Congress stalwarts questioned the strategic timing, panicked over Western sanctions, and pushed for capitulation to discriminatory international regimes like the CTBT.   Aborting the 1995 test under CIA surveillance had already humiliated Indian strategic capability; the opposition’s behavior in 1998 revealed their utter willingness to compromise national defense to appease foreign powers. Had these obstructionist forces succeeded in derailing Pokhran-II, India would have been permanently disarmed, trapped in subservience, and rendered defenseless against nuclear encirclement.</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/history-of-it/story/pokhran-nuclear-test-1995-smiling-buddha-1998-us-spy-satellites-india-abort-us-saudi-nuclear-deal-2954767-2026-07-24</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/india/story/how-india-sprung-back-after-us-sanctions-atal-bihari-vajpayee-trump-modi-nuclear-test-tariffs-2777642-2025-08-28</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/1N9UNqkails</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/PoliticalKida/videos/congress-was-not-happy-with-indias-nuclear-test-in-1998/735959812414227/</t>
   </si>
 </sst>
 </file>
@@ -267,7 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -277,6 +310,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -340,10 +376,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L6" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L6">
-    <sortCondition ref="A1:A6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L7" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L7">
+    <sortCondition ref="A1:A7"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{36410997-4BAE-4139-BA6C-527DB552268B}" name="Year" dataDxfId="11"/>
@@ -648,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B667CDE-8E2B-439F-AECC-B04A1264504F}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -741,179 +777,221 @@
     </row>
     <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>1998</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="330" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="330" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="330" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>2026</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="2"/>
+      <c r="L6" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="285" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:12" ht="285" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K3" r:id="rId1" xr:uid="{4965CF61-9FBF-4AB1-B4DB-A24E0EBC9E1C}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{A4A78A15-6AD2-4DFF-9ACA-0319D684CDB3}"/>
-    <hyperlink ref="J3" r:id="rId3" xr:uid="{C47B8228-DBBC-417E-A50D-F19171914C13}"/>
-    <hyperlink ref="L3" r:id="rId4" xr:uid="{8006A57B-4B38-4A73-9A4C-97AB78A24E42}"/>
-    <hyperlink ref="J4" r:id="rId5" xr:uid="{D275290F-CEEE-424A-BD8F-8B4197582A5B}"/>
-    <hyperlink ref="K4" r:id="rId6" xr:uid="{94922FC6-1ADA-4B6D-BCE6-3B5B1A25A268}"/>
-    <hyperlink ref="L4" r:id="rId7" xr:uid="{D8963F0D-EE85-4A56-8895-01CED52D48D7}"/>
-    <hyperlink ref="I4" r:id="rId8" xr:uid="{CFCA3D52-DBAA-486C-9AFA-F939D4E8CAB8}"/>
-    <hyperlink ref="I5" r:id="rId9" xr:uid="{E2C8669E-DD8D-4A51-8D15-D96255441B18}"/>
-    <hyperlink ref="J5" r:id="rId10" xr:uid="{83BA019D-EA6C-4D87-8F69-1252DAABDB5A}"/>
-    <hyperlink ref="K5" r:id="rId11" xr:uid="{B1805763-2E1D-42D9-ADCF-E25B4A02451E}"/>
-    <hyperlink ref="L6" r:id="rId12" xr:uid="{869838BC-C3E3-45CD-B30E-81BED2D3933C}"/>
-    <hyperlink ref="K6" r:id="rId13" xr:uid="{BD85F19F-41C3-4AD6-A213-E870C7A32A47}"/>
-    <hyperlink ref="J6" r:id="rId14" xr:uid="{1BFE7085-12C3-4CBA-B944-21FEFC85C2BF}"/>
-    <hyperlink ref="I6" r:id="rId15" xr:uid="{5DAC2B73-C720-4395-A8CA-A8ADA64F28E1}"/>
+    <hyperlink ref="K4" r:id="rId1" xr:uid="{4965CF61-9FBF-4AB1-B4DB-A24E0EBC9E1C}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{A4A78A15-6AD2-4DFF-9ACA-0319D684CDB3}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{C47B8228-DBBC-417E-A50D-F19171914C13}"/>
+    <hyperlink ref="L4" r:id="rId4" xr:uid="{8006A57B-4B38-4A73-9A4C-97AB78A24E42}"/>
+    <hyperlink ref="J5" r:id="rId5" xr:uid="{D275290F-CEEE-424A-BD8F-8B4197582A5B}"/>
+    <hyperlink ref="K5" r:id="rId6" xr:uid="{94922FC6-1ADA-4B6D-BCE6-3B5B1A25A268}"/>
+    <hyperlink ref="L5" r:id="rId7" xr:uid="{D8963F0D-EE85-4A56-8895-01CED52D48D7}"/>
+    <hyperlink ref="I5" r:id="rId8" xr:uid="{CFCA3D52-DBAA-486C-9AFA-F939D4E8CAB8}"/>
+    <hyperlink ref="I6" r:id="rId9" xr:uid="{E2C8669E-DD8D-4A51-8D15-D96255441B18}"/>
+    <hyperlink ref="J6" r:id="rId10" xr:uid="{83BA019D-EA6C-4D87-8F69-1252DAABDB5A}"/>
+    <hyperlink ref="K6" r:id="rId11" xr:uid="{B1805763-2E1D-42D9-ADCF-E25B4A02451E}"/>
+    <hyperlink ref="L7" r:id="rId12" xr:uid="{869838BC-C3E3-45CD-B30E-81BED2D3933C}"/>
+    <hyperlink ref="K7" r:id="rId13" xr:uid="{BD85F19F-41C3-4AD6-A213-E870C7A32A47}"/>
+    <hyperlink ref="J7" r:id="rId14" xr:uid="{1BFE7085-12C3-4CBA-B944-21FEFC85C2BF}"/>
+    <hyperlink ref="I7" r:id="rId15" xr:uid="{5DAC2B73-C720-4395-A8CA-A8ADA64F28E1}"/>
     <hyperlink ref="K2" r:id="rId16" xr:uid="{6E753CA4-545C-44D7-96F1-5BB67BA545B2}"/>
     <hyperlink ref="L2" r:id="rId17" xr:uid="{2998BFA7-0E72-421E-B188-FC558D33BFF9}"/>
     <hyperlink ref="J2" r:id="rId18" xr:uid="{D3AD9D0E-8F7C-4AA3-AEB3-B998249D1FFE}"/>
     <hyperlink ref="I2" r:id="rId19" xr:uid="{F989E7E7-D239-4F06-B64F-7D54481F0111}"/>
+    <hyperlink ref="L3" r:id="rId20" xr:uid="{EAC3CDCB-C9F5-4145-844D-20F5B548EF96}"/>
+    <hyperlink ref="K3" r:id="rId21" xr:uid="{46A508B0-AA79-43CC-8B50-929A7B0DD4B5}"/>
+    <hyperlink ref="J3" r:id="rId22" xr:uid="{0DD18D57-2C23-4240-8308-FDA965AD61EF}"/>
+    <hyperlink ref="I3" r:id="rId23" xr:uid="{926982EC-4ED6-4012-95F2-6F2DFD642BC9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/India_300_National_Initiatives_History_2_2.xlsx
+++ b/data/India_300_National_Initiatives_History_2_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6AA440-0A65-474E-9524-22812B7790A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0437DB4B-B7B3-4E38-BE54-4347A14B6372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,15 +133,9 @@
     <t>The deliberate sabotage engineered by the Congress, Left parties, and their allied ecosystem inflicted severe harm on India’s momentum. By dragging a critical national infrastructure project through legal quagmires, these obstructionist elements directly bled public funds, forced the exchequer to waste thousands of crores on dilapidated rented offices, and paralyzed administrative synergy. Their agenda sought to keep Indian democracy trapped inside decrepit, unsafe colonial relics just to score petty political points. Stalling the heart of Indian governance during critical years exposed their sheer hostility toward India shedding its subservient colonial baggage and asserting itself on the global stage.</t>
   </si>
   <si>
-    <t>Congress, CPI(M), CPI, TMC, AAP, DMK, RJD, SP, NCP, Shiv Sena (UBT), activist NGOs, Pseudo-Environmentalist Lobbies</t>
-  </si>
-  <si>
     <t>It obliterated a toxic relic of partition and realized the sacred vision of "Ek Vidhan, Ek Nishan, Ek Pradhan." Article 370 was an artificial constitutional barricade that bred cross-border separatism, shielded terror networks, and robbed women, Dalits, and marginalized communities of core constitutional protections like reservations and equal property rights. By smashing this discriminatory wall, India fully integrated Jammu &amp; Kashmir into the Union, crushing decades of dynastic loot and anti-national blackmail. It unleashed grass-roots democracy via Panchayati Raj, triggered record investments, tourism, and infrastructure growth, and restored sovereign authority over the nation's crown jewel. The abrogation permanently cemented Bharat's territorial integrity and proved that India will never compromise on its sovereignty.</t>
   </si>
   <si>
-    <t>Congress, CPI(M), CPI, NC, PDP, TMC, DMK, AAP, SP, RJD, People's Union for Civil Liberties, activist NGOs</t>
-  </si>
-  <si>
     <t>Over twenty-three petitions were filed by opposition politicians, separatist sympathizers, and activist outfits in the Supreme Court, desperately challenging Presidential Orders CO 272 and CO 273, the exercise of powers under President’s Rule, and the state's bifurcation. They falsely argued that Article 370 had acquired permanent status, attempting to stall national integration through protracted constitutional litigation.</t>
   </si>
   <si>
@@ -158,9 +152,6 @@
   </si>
   <si>
     <t>Over 200 petitions were filed in the Supreme Court by opposition leaders, radical outfits, and activist lawyers. They weaponized Article 14, peddled bogus claims of religious discrimination, and filed serial stay applications to paralyze the law and block rule notification.</t>
-  </si>
-  <si>
-    <t>Congress, TMC, CPI(M), CPI, AAP, DMK, SP, RJD, AIMIM, IUML, left-leaning student groups, foreign-funded activist NGOs</t>
   </si>
   <si>
     <t>National sovereignty and humanitarian resolve prevailed: the Supreme Court repeatedly refused to stay the Act or its rules. The Union Government notified the CAA Rules, operationalized fast-track digital portals, and began issuing citizenship certificates across India.</t>
@@ -176,9 +167,6 @@
     <t>It is India’s non-negotiable maritime fortress and an unsinkable aircraft carrier guarding the entrance to the Malacca Strait. Dominating the Six Degree Channel—where global energy arteries pass—it decisively smashes China’s belligerent "String of Pearls" encirclement and counters hostile PLAN submarine aggression. Integrating an International Container Transhipment Port at Galathea Bay, a joint civil-military dual-use international air base, and power infrastructure, it turns the Andaman &amp; Nicobar Tri-Services Command into an unbreachable maritime sentinel. Economically, it frees Indian trade from humiliating dependence on foreign transhipment hubs like Colombo and Singapore, retaining billions of dollars in sovereign revenue.</t>
   </si>
   <si>
-    <t>Congress, CPI(M), CPI, TMC, DMK, AAP, activist NGOs, foreign-funded green lobbies</t>
-  </si>
-  <si>
     <t>Obstructionist petitions were filed before the National Green Tribunal, Calcutta High Court, and Supreme Court. Opponents weaponized Coastal Regulation Zone norms, biological diversity concerns, and Forest Rights Act disputes to demand blanket stays, aiming to completely paralyze vital military-civilian construction.</t>
   </si>
   <si>
@@ -198,9 +186,6 @@
     <t>It is the unshakeable lifeline of Western India and a cornerstone of national security, food sovereignty, and economic survival. By taming the Narmada, it eradicated parched, drought-ridden desperation across Saurashtra, Kutch, and arid belts of Rajasthan, channeling life-saving drinking water directly to forward defense deployments and BSF border outposts along the hostile Indo-Pak frontier. Generating 1,450 MW of clean hydroelectric power and irrigating over 18 lakh hectares of barren land, it transformed chronic famine zones into agricultural powerhouses. It insulated critical border populations from destabilizing water crises, permanently securing national resource resilience.</t>
   </si>
   <si>
-    <t>Congress, CPI(M), CPI, Left Front, Narmada Bachao Andolan, foreign-funded activist NGOs, pseudo-environmentalist lobbies,</t>
-  </si>
-  <si>
     <t>Opponents and activist networks dragged the project into the Supreme Court and international tribunals, weaponizing PILs to allege human rights abuses, rehabilitation inadequacies, and seismic hazards. They secured an injunction that halted construction between 1995 and 1999, attempting to permanently freeze work.</t>
   </si>
   <si>
@@ -231,9 +216,6 @@
     <t>It is the non-negotiable bedrock of India’s national security, strategic autonomy, and sovereign survival. Flanked by two colluding, hostile nuclear-armed adversaries—an expansionist China and an export hub of cross-border jihad in Pakistan—India faced an existential security dilemma. The Pokhran tests obliterated hypocritical global nuclear apartheid, smashed the discriminatory non-proliferation monopoly of the P-5 powers, and erected an impenetrable shield of credible strategic deterrence.   Operation Shakti liberated India from decades of foreign intimidation and atomic blackmail. It validated thermonuclear, fission, and sub-kiloton weapon designs, directly birthing an unassailable strategic nuclear triad across land, air, and sea. Anchored by the doctrine of Credible Minimum Deterrence and No First Use, it ensured that no hostile power can ever contemplate waging war against Indian soil without facing guaranteed, catastrophic retaliation. It established that the defense of 1.4 billion citizens will never be mortgaged to foreign capitals.</t>
   </si>
   <si>
-    <t>Congress, CPI(M), CPI, Left Front, Samajwadi Party, Movement in India for Nuclear Disarmament, foreign-funded anti-nuclear activist NGOs</t>
-  </si>
-  <si>
     <t>Discriminatory global treaties—the Nuclear Non-Proliferation Treaty (NPT) and the Comprehensive Nuclear-Test-Ban Treaty (CTBT)—were weaponized internationally to encircle and legally suffocate India’s indigenous nuclear deterrent. Major powers triggered automatic punitive statutes, notably the US Glenn and Symington Amendments, slapping blanket economic and high-technology export embargoes. Simultaneously, United Nations Security Council Resolution 1172 was enacted to legally coerce India into rolling back its nuclear weapons programme, halting missile delivery development, and surrendering its sovereign strategic defense.</t>
   </si>
   <si>
@@ -256,6 +238,24 @@
   </si>
   <si>
     <t>https://www.facebook.com/PoliticalKida/videos/congress-was-not-happy-with-indias-nuclear-test-in-1998/735959812414227/</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, Left Front, Narmada Bachao Andolan, Foreign-funded Activist NGOs, Pseudo-Environmentalist</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, Left Front, Samajwadi Party, Movement in India for Nuclear Disarmament, Foreign-Funded Anti-Nuclear Activist NGOs</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, NC, PDP, TMC, DMK, AAP, SP, RJD, People's Union for Civil Liberties, Foreign-funded Activist NGOs</t>
+  </si>
+  <si>
+    <t>Congress, TMC, CPI(M), CPI, AAP, DMK, SP, RJD, AIMIM, IUML, Left-Leaning Student Groups, Foreign-funded Activist NGOs</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, DMK, AAP, activist NGOs, Foreign-funded Activist NGOs</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, AAP, DMK, RJD, SP, NCP, Shiv Sena (UBT), Foreign-funded Activist NGOs, Pseudo-Environmentalist</t>
   </si>
 </sst>
 </file>
@@ -742,37 +742,37 @@
         <v>1961</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -780,37 +780,37 @@
         <v>1998</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -821,22 +821,22 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>16</v>
@@ -859,22 +859,22 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>23</v>
@@ -897,22 +897,22 @@
         <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>25</v>
@@ -936,7 +936,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
